--- a/frontend/public/template-files/monthly-financial-statement-review-template.xlsx
+++ b/frontend/public/template-files/monthly-financial-statement-review-template.xlsx
@@ -511,21 +511,21 @@
   <dxfs count="3">
     <dxf>
       <font>
+        <color rgb="FFD97706"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFDC2626"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD97706"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
     </dxf>

--- a/frontend/public/template-files/monthly-financial-statement-review-template.xlsx
+++ b/frontend/public/template-files/monthly-financial-statement-review-template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="105">
   <si>
     <t>Monthly Financial Statement Review</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Taylor Morgan</t>
   </si>
   <si>
-    <t>Review Date</t>
+    <t>Completion Date</t>
   </si>
   <si>
     <t>Input Mode</t>
@@ -66,7 +66,7 @@
     <t>1. Confirm client, period, preparer, input mode, and materiality settings.</t>
   </si>
   <si>
-    <t>2. Paste a trial balance or enter it manually in the blue input table.</t>
+    <t>2. Paste a monthly financial statement or enter it manually in the blue input table.</t>
   </si>
   <si>
     <t>3. Review formula-driven period and budget variances; document exceptions.</t>
@@ -99,7 +99,7 @@
     <t>Review item or failed control</t>
   </si>
   <si>
-    <t>Paste Import — Monthly Trial Balance</t>
+    <t>Paste Import - Monthly Financial Statement</t>
   </si>
   <si>
     <t>Enter or paste values in blue cells. Do not add rows beyond row 105.</t>
@@ -129,7 +129,7 @@
     <t>Review Category</t>
   </si>
   <si>
-    <t>Income Statement</t>
+    <t>Profit and Loss</t>
   </si>
   <si>
     <t>4000</t>
@@ -249,7 +249,7 @@
     <t>Sales Tax Payable</t>
   </si>
   <si>
-    <t>Manual Input — Monthly Trial Balance</t>
+    <t>Manual Input - Monthly Financial Statement</t>
   </si>
   <si>
     <t>Formula-driven comparison. Add reviewer notes only in column N.</t>
@@ -282,7 +282,7 @@
     <t>Exception Score</t>
   </si>
   <si>
-    <t>Monthly Financial Review — Executive Summary</t>
+    <t>Monthly Financial Review - Executive Summary</t>
   </si>
   <si>
     <t>Decision-ready KPIs and the five largest exceptions</t>
@@ -469,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -497,6 +497,7 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3849,7 +3850,7 @@
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A6,'Manual Input'!A6)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B6,'Manual Input'!B6)</f>
@@ -3908,7 +3909,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A7,'Manual Input'!A7)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B7" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B7,'Manual Input'!B7)</f>
@@ -3967,7 +3968,7 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A8,'Manual Input'!A8)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B8" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B8,'Manual Input'!B8)</f>
@@ -4026,7 +4027,7 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A9,'Manual Input'!A9)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B9" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B9,'Manual Input'!B9)</f>
@@ -4085,7 +4086,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A10,'Manual Input'!A10)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B10,'Manual Input'!B10)</f>
@@ -4144,7 +4145,7 @@
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!A11,'Manual Input'!A11)</f>
-        <v>Income Statement</v>
+        <v>Profit and Loss</v>
       </c>
       <c r="B11" s="14" t="str">
         <f>IF('Start Here'!$B$8="Paste Import",'Paste Import'!B11,'Manual Input'!B11)</f>
@@ -9829,9 +9830,9 @@
       <c r="C5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="18" t="str">
+      <c r="D5" s="19">
         <f>'Start Here'!B5</f>
-        <v>2026-06-30</v>
+        <v>46203</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>4</v>
@@ -9843,108 +9844,116 @@
       <c r="G5" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="19" t="str">
+      <c r="H5" s="20" t="str">
         <f>IF(D12=0,"Complete","Review")</f>
         <v>Review</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="19">
+        <f>'Start Here'!B7</f>
+        <v>46213</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="18"/>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>91</v>
       </c>
       <c r="D8" s="18"/>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>92</v>
       </c>
       <c r="F8" s="18"/>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+      <c r="A9" s="22">
         <f>SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Revenue")</f>
         <v>303000</v>
       </c>
       <c r="B9" s="18"/>
-      <c r="C9" s="21">
-        <f>B8-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Cost of Goods Sold")</f>
+      <c r="C9" s="22">
+        <f>A9-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Cost of Goods Sold")</f>
         <v>212000</v>
       </c>
       <c r="D9" s="18"/>
-      <c r="E9" s="21">
-        <f>D8-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Operating Expense")</f>
+      <c r="E9" s="22">
+        <f>C9-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Operating Expense")</f>
         <v>90000</v>
       </c>
       <c r="F9" s="18"/>
-      <c r="G9" s="21">
-        <f>F8+SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Other Income")-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Other Expense")</f>
+      <c r="G9" s="22">
+        <f>E9+SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Other Income")-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Other Expense")</f>
         <v>90000</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>94</v>
       </c>
       <c r="B11" s="18"/>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+      <c r="A12" s="22">
         <f>SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Cash")+SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Accounts Receivable")+SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Current Assets")-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Accounts Payable")-SUMIFS('Review'!$E$6:$E$105,'Review'!$L$6:$L$105,"Current Liabilities")</f>
         <v>130000</v>
       </c>
       <c r="B12" s="18"/>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>COUNTIF('Review'!$M$6:$M$105,"Review")+COUNTIF('Review'!$M$6:$M$105,"Incomplete")</f>
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="25" t="s">
         <v>100</v>
       </c>
     </row>
@@ -9960,15 +9969,15 @@
         <f>IFERROR(INDEX('Review'!$L$6:$L$105,MATCH(LARGE('Review'!$O$6:$O$105,1),'Review'!$O$6:$O$105,0)),"")</f>
         <v>Revenue</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>IFERROR(INDEX('Review'!$E$6:$E$105,MATCH(LARGE('Review'!$O$6:$O$105,1),'Review'!$O$6:$O$105,0)),"")</f>
         <v>58000</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>IFERROR(INDEX('Review'!$H$6:$H$105,MATCH(LARGE('Review'!$O$6:$O$105,1),'Review'!$O$6:$O$105,0)),"")</f>
         <v>58000</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>IFERROR(INDEX('Review'!$J$6:$J$105,MATCH(LARGE('Review'!$O$6:$O$105,1),'Review'!$O$6:$O$105,0)),"")</f>
         <v>13000</v>
       </c>
@@ -9993,15 +10002,15 @@
         <f>IFERROR(INDEX('Review'!$L$6:$L$105,MATCH(LARGE('Review'!$O$6:$O$105,2),'Review'!$O$6:$O$105,0)),"")</f>
         <v>Revenue</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>IFERROR(INDEX('Review'!$E$6:$E$105,MATCH(LARGE('Review'!$O$6:$O$105,2),'Review'!$O$6:$O$105,0)),"")</f>
         <v>245000</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>IFERROR(INDEX('Review'!$H$6:$H$105,MATCH(LARGE('Review'!$O$6:$O$105,2),'Review'!$O$6:$O$105,0)),"")</f>
         <v>35000</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>IFERROR(INDEX('Review'!$J$6:$J$105,MATCH(LARGE('Review'!$O$6:$O$105,2),'Review'!$O$6:$O$105,0)),"")</f>
         <v>15000</v>
       </c>
@@ -10026,15 +10035,15 @@
         <f>IFERROR(INDEX('Review'!$L$6:$L$105,MATCH(LARGE('Review'!$O$6:$O$105,3),'Review'!$O$6:$O$105,0)),"")</f>
         <v>Cash</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <f>IFERROR(INDEX('Review'!$E$6:$E$105,MATCH(LARGE('Review'!$O$6:$O$105,3),'Review'!$O$6:$O$105,0)),"")</f>
         <v>122000</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <f>IFERROR(INDEX('Review'!$H$6:$H$105,MATCH(LARGE('Review'!$O$6:$O$105,3),'Review'!$O$6:$O$105,0)),"")</f>
         <v>26000</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <f>IFERROR(INDEX('Review'!$J$6:$J$105,MATCH(LARGE('Review'!$O$6:$O$105,3),'Review'!$O$6:$O$105,0)),"")</f>
         <v>12000</v>
       </c>
@@ -10059,15 +10068,15 @@
         <f>IFERROR(INDEX('Review'!$L$6:$L$105,MATCH(LARGE('Review'!$O$6:$O$105,4),'Review'!$O$6:$O$105,0)),"")</f>
         <v>Accounts Receivable</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <f>IFERROR(INDEX('Review'!$E$6:$E$105,MATCH(LARGE('Review'!$O$6:$O$105,4),'Review'!$O$6:$O$105,0)),"")</f>
         <v>87000</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>IFERROR(INDEX('Review'!$H$6:$H$105,MATCH(LARGE('Review'!$O$6:$O$105,4),'Review'!$O$6:$O$105,0)),"")</f>
         <v>15000</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>IFERROR(INDEX('Review'!$J$6:$J$105,MATCH(LARGE('Review'!$O$6:$O$105,4),'Review'!$O$6:$O$105,0)),"")</f>
         <v>11000</v>
       </c>
@@ -10092,15 +10101,15 @@
         <f>IFERROR(INDEX('Review'!$L$6:$L$105,MATCH(LARGE('Review'!$O$6:$O$105,5),'Review'!$O$6:$O$105,0)),"")</f>
         <v>Operating Expense</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>IFERROR(INDEX('Review'!$E$6:$E$105,MATCH(LARGE('Review'!$O$6:$O$105,5),'Review'!$O$6:$O$105,0)),"")</f>
         <v>31000</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>IFERROR(INDEX('Review'!$H$6:$H$105,MATCH(LARGE('Review'!$O$6:$O$105,5),'Review'!$O$6:$O$105,0)),"")</f>
         <v>12000</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>IFERROR(INDEX('Review'!$J$6:$J$105,MATCH(LARGE('Review'!$O$6:$O$105,5),'Review'!$O$6:$O$105,0)),"")</f>
         <v>11000</v>
       </c>
